--- a/vlookup file for practice (1).xlsx
+++ b/vlookup file for practice (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucky\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucky\Desktop\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7E505F-F9A9-43E1-84B5-1E03B0BE765E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A8CCDE-C0F5-452C-B112-C0370406805F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="13500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="V_LOOKUP" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'V_LOOKUP 6'!$A$1:$C$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -520,7 +533,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
@@ -529,40 +542,49 @@
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Impact"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Impact"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
       <name val="Impact"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -645,7 +667,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="29">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -708,12 +730,60 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF00B0F0"/>
           <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA8D08D"/>
+          <bgColor rgb="FFA8D08D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE598"/>
+          <bgColor rgb="FFFFE598"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA8D08D"/>
+          <bgColor rgb="FFA8D08D"/>
         </patternFill>
       </fill>
     </dxf>
@@ -784,24 +854,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFA8D08D"/>
           <bgColor rgb="FFA8D08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -834,110 +888,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF00B0F0"/>
           <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA8D08D"/>
-          <bgColor rgb="FFA8D08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA8D08D"/>
-          <bgColor rgb="FFA8D08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA8D08D"/>
-          <bgColor rgb="FFA8D08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA8D08D"/>
-          <bgColor rgb="FFA8D08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE598"/>
-          <bgColor rgb="FFFFE598"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1279,14 +1229,13 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="3" width="9.375" customWidth="1"/>
@@ -1299,7 +1248,7 @@
     <col min="11" max="11" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1326,7 +1275,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="14.25" customHeight="1">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>5600001</v>
       </c>
@@ -1353,7 +1302,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>5600002</v>
       </c>
@@ -1380,7 +1329,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>5600003</v>
       </c>
@@ -1407,7 +1356,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>5600004</v>
       </c>
@@ -1434,7 +1383,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="14.25" customHeight="1">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5600005</v>
       </c>
@@ -1459,7 +1408,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5600006</v>
       </c>
@@ -1484,7 +1433,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="14.25" customHeight="1">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5600007</v>
       </c>
@@ -1514,7 +1463,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5600008</v>
       </c>
@@ -1541,7 +1490,7 @@
       <c r="J9" s="7"/>
       <c r="K9" s="8"/>
     </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5600009</v>
       </c>
@@ -1568,7 +1517,7 @@
       <c r="J10" s="7"/>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>5600010</v>
       </c>
@@ -1595,7 +1544,7 @@
       <c r="J11" s="7"/>
       <c r="K11" s="8"/>
     </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>5600011</v>
       </c>
@@ -1622,7 +1571,7 @@
       <c r="J12" s="7"/>
       <c r="K12" s="8"/>
     </row>
-    <row r="13" spans="1:11" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>5600012</v>
       </c>
@@ -1647,7 +1596,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="14.25" customHeight="1">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>5600013</v>
       </c>
@@ -1672,7 +1621,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" ht="14.25" customHeight="1">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>5600014</v>
       </c>
@@ -1699,7 +1648,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="14.25" customHeight="1">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>5600015</v>
       </c>
@@ -1726,7 +1675,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" ht="14.25" customHeight="1">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>5600016</v>
       </c>
@@ -1753,7 +1702,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" ht="14.25" customHeight="1">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>5600017</v>
       </c>
@@ -1780,7 +1729,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" ht="14.25" customHeight="1">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1795,7 +1744,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" ht="14.25" customHeight="1">
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1808,7 +1757,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" ht="14.25" customHeight="1">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>0</v>
       </c>
@@ -1831,24 +1780,24 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" ht="14.25" customHeight="1">
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>5600015</v>
       </c>
       <c r="B22" s="2">
-        <f>INDEX($B$2:$E$18,MATCH($A22,$F$2:$F$18,0),MATCH(B$21,$B$1:$E$1,0))</f>
+        <f t="shared" ref="B22:B27" si="0">INDEX($B$2:$E$18,MATCH($A22,$F$2:$F$18,0),MATCH(B$21,$B$1:$E$1,0))</f>
         <v>4690</v>
       </c>
       <c r="C22" s="2" t="str">
-        <f t="shared" ref="C22:E25" si="0">INDEX($B$2:$E$18,MATCH($A22,$F$2:$F$18,0),MATCH(C$21,$B$1:$E$1,0))</f>
+        <f t="shared" ref="C22:E25" si="1">INDEX($B$2:$E$18,MATCH($A22,$F$2:$F$18,0),MATCH(C$21,$B$1:$E$1,0))</f>
         <v>Checking</v>
       </c>
       <c r="D22" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>North County</v>
       </c>
       <c r="E22" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>New</v>
       </c>
       <c r="F22" s="2"/>
@@ -1858,24 +1807,24 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" ht="14.25" customHeight="1">
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>5600012</v>
       </c>
       <c r="B23" s="2">
-        <f>INDEX($B$2:$E$18,MATCH($A23,$F$2:$F$18,0),MATCH(B$21,$B$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>6837</v>
       </c>
       <c r="C23" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Savings</v>
       </c>
       <c r="D23" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Westside</v>
       </c>
       <c r="E23" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Existing</v>
       </c>
       <c r="F23" s="2"/>
@@ -1885,24 +1834,24 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" ht="14.25" customHeight="1">
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>5600010</v>
       </c>
       <c r="B24" s="2">
-        <f>INDEX($B$2:$E$18,MATCH($A24,$F$2:$F$18,0),MATCH(B$21,$B$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>12000</v>
       </c>
       <c r="C24" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CD</v>
       </c>
       <c r="D24" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Westside</v>
       </c>
       <c r="E24" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Existing</v>
       </c>
       <c r="F24" s="2"/>
@@ -1912,24 +1861,24 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="14.25" customHeight="1">
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>5600015</v>
       </c>
       <c r="B25" s="2">
-        <f>INDEX($B$2:$E$18,MATCH($A25,$F$2:$F$18,0),MATCH(B$21,$B$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>4690</v>
       </c>
       <c r="C25" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Checking</v>
       </c>
       <c r="D25" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>North County</v>
       </c>
       <c r="E25" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>New</v>
       </c>
       <c r="F25" s="2"/>
@@ -1939,12 +1888,12 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" ht="14.25" customHeight="1">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>5600014</v>
       </c>
       <c r="B26" s="2">
-        <f>INDEX($B$2:$E$18,MATCH($A26,$F$2:$F$18,0),MATCH(B$21,$B$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>5000</v>
       </c>
       <c r="C26" s="2"/>
@@ -1957,24 +1906,24 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" ht="14.25" customHeight="1">
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>5600009</v>
       </c>
       <c r="B27" s="2">
-        <f>INDEX($B$2:$E$18,MATCH($A27,$F$2:$F$18,0),MATCH(B$21,$B$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>15000</v>
       </c>
       <c r="C27" s="2" t="str">
-        <f t="shared" ref="C27:E27" si="1">INDEX($B$2:$E$18,MATCH($A27,$F$2:$F$18,0),MATCH(C$21,$B$1:$E$1,0))</f>
+        <f t="shared" ref="C27:E27" si="2">INDEX($B$2:$E$18,MATCH($A27,$F$2:$F$18,0),MATCH(C$21,$B$1:$E$1,0))</f>
         <v>CD</v>
       </c>
       <c r="D27" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Westside</v>
       </c>
       <c r="E27" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Existing</v>
       </c>
       <c r="F27" s="2"/>
@@ -1984,10 +1933,10 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" ht="14.25" customHeight="1">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="e">
-        <f t="shared" ref="B23:B29" si="2">INDEX($B$2:$E$18,MATCH($A$22,$F$2:$F$18,0),MATCH(B27,$B$1:$E$1,0))</f>
+        <f t="shared" ref="B28:B29" si="3">INDEX($B$2:$E$18,MATCH($A$22,$F$2:$F$18,0),MATCH(B27,$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
       <c r="C28" s="2"/>
@@ -2000,10 +1949,10 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" ht="14.25" customHeight="1">
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="C29" s="2"/>
@@ -2016,7 +1965,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2029,7 +1978,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" ht="14.25" customHeight="1">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2042,7 +1991,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11" ht="14.25" customHeight="1">
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2055,7 +2004,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2068,7 +2017,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1">
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2081,7 +2030,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1">
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2094,7 +2043,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1">
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2107,7 +2056,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1">
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2120,7 +2069,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" ht="14.25" customHeight="1">
+    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2133,7 +2082,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" ht="14.25" customHeight="1">
+    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2146,7 +2095,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" ht="14.25" customHeight="1">
+    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2159,7 +2108,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" ht="14.25" customHeight="1">
+    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2172,7 +2121,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" ht="14.25" customHeight="1">
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2185,7 +2134,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" ht="14.25" customHeight="1">
+    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2198,7 +2147,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" ht="14.25" customHeight="1">
+    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2211,7 +2160,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" ht="14.25" customHeight="1">
+    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2224,7 +2173,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" ht="14.25" customHeight="1">
+    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2237,7 +2186,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" ht="14.25" customHeight="1">
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -2250,7 +2199,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11" ht="14.25" customHeight="1">
+    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2263,7 +2212,7 @@
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11" ht="14.25" customHeight="1">
+    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2276,7 +2225,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" ht="14.25" customHeight="1">
+    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2289,7 +2238,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11" ht="14.25" customHeight="1">
+    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2302,7 +2251,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11" ht="14.25" customHeight="1">
+    <row r="52" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -2315,7 +2264,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11" ht="14.25" customHeight="1">
+    <row r="53" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2328,7 +2277,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11" ht="14.25" customHeight="1">
+    <row r="54" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2341,7 +2290,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11" ht="14.25" customHeight="1">
+    <row r="55" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2354,7 +2303,7 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:11" ht="14.25" customHeight="1">
+    <row r="56" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2367,7 +2316,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11" ht="14.25" customHeight="1">
+    <row r="57" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2380,7 +2329,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11" ht="14.25" customHeight="1">
+    <row r="58" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2393,7 +2342,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11" ht="14.25" customHeight="1">
+    <row r="59" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2406,7 +2355,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11" ht="14.25" customHeight="1">
+    <row r="60" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -2419,7 +2368,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11" ht="14.25" customHeight="1">
+    <row r="61" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2432,7 +2381,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11" ht="14.25" customHeight="1">
+    <row r="62" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -2445,7 +2394,7 @@
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11" ht="14.25" customHeight="1">
+    <row r="63" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -2458,7 +2407,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11" ht="14.25" customHeight="1">
+    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -2471,7 +2420,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11" ht="14.25" customHeight="1">
+    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2484,7 +2433,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11" ht="14.25" customHeight="1">
+    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -2497,7 +2446,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:11" ht="14.25" customHeight="1">
+    <row r="67" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2510,7 +2459,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11" ht="14.25" customHeight="1">
+    <row r="68" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -2523,7 +2472,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11" ht="14.25" customHeight="1">
+    <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2536,7 +2485,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:11" ht="14.25" customHeight="1">
+    <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -2549,7 +2498,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:11" ht="14.25" customHeight="1">
+    <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -2562,7 +2511,7 @@
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="1:11" ht="14.25" customHeight="1">
+    <row r="72" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -2575,7 +2524,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" ht="14.25" customHeight="1">
+    <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -2588,7 +2537,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:11" ht="14.25" customHeight="1">
+    <row r="74" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -2601,7 +2550,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" ht="14.25" customHeight="1">
+    <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2614,7 +2563,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" ht="14.25" customHeight="1">
+    <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -2627,7 +2576,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:11" ht="14.25" customHeight="1">
+    <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -2640,7 +2589,7 @@
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="1:11" ht="14.25" customHeight="1">
+    <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -2653,7 +2602,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1">
+    <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -2666,7 +2615,7 @@
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="1:11" ht="14.25" customHeight="1">
+    <row r="80" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2679,7 +2628,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11" ht="14.25" customHeight="1">
+    <row r="81" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -2692,7 +2641,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" ht="14.25" customHeight="1">
+    <row r="82" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -2705,7 +2654,7 @@
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
     </row>
-    <row r="83" spans="1:11" ht="14.25" customHeight="1">
+    <row r="83" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -2718,7 +2667,7 @@
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
     </row>
-    <row r="84" spans="1:11" ht="14.25" customHeight="1">
+    <row r="84" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -2731,7 +2680,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
     </row>
-    <row r="85" spans="1:11" ht="14.25" customHeight="1">
+    <row r="85" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2744,7 +2693,7 @@
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
     </row>
-    <row r="86" spans="1:11" ht="14.25" customHeight="1">
+    <row r="86" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -2757,7 +2706,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="1:11" ht="14.25" customHeight="1">
+    <row r="87" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -2770,7 +2719,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
     </row>
-    <row r="88" spans="1:11" ht="14.25" customHeight="1">
+    <row r="88" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2783,7 +2732,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
     </row>
-    <row r="89" spans="1:11" ht="14.25" customHeight="1">
+    <row r="89" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -2796,7 +2745,7 @@
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
     </row>
-    <row r="90" spans="1:11" ht="14.25" customHeight="1">
+    <row r="90" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -2809,7 +2758,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
     </row>
-    <row r="91" spans="1:11" ht="14.25" customHeight="1">
+    <row r="91" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -2822,7 +2771,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
     </row>
-    <row r="92" spans="1:11" ht="14.25" customHeight="1">
+    <row r="92" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -2835,7 +2784,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
     </row>
-    <row r="93" spans="1:11" ht="14.25" customHeight="1">
+    <row r="93" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -2848,7 +2797,7 @@
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
     </row>
-    <row r="94" spans="1:11" ht="14.25" customHeight="1">
+    <row r="94" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -2861,7 +2810,7 @@
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
     </row>
-    <row r="95" spans="1:11" ht="14.25" customHeight="1">
+    <row r="95" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -2874,7 +2823,7 @@
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
     </row>
-    <row r="96" spans="1:11" ht="14.25" customHeight="1">
+    <row r="96" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -2887,7 +2836,7 @@
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
     </row>
-    <row r="97" spans="1:11" ht="14.25" customHeight="1">
+    <row r="97" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -2900,7 +2849,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
     </row>
-    <row r="98" spans="1:11" ht="14.25" customHeight="1">
+    <row r="98" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -2913,7 +2862,7 @@
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
     </row>
-    <row r="99" spans="1:11" ht="14.25" customHeight="1">
+    <row r="99" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -2926,7 +2875,7 @@
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
     </row>
-    <row r="100" spans="1:11" ht="14.25" customHeight="1">
+    <row r="100" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -2940,119 +2889,90 @@
       <c r="K100" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B18">
-    <cfRule type="expression" dxfId="28" priority="25">
+  <conditionalFormatting sqref="A2:A18">
+    <cfRule type="expression" dxfId="19" priority="26">
       <formula>MAX($B$2:$B$18)=$B2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A18">
-    <cfRule type="expression" dxfId="27" priority="26">
+  <conditionalFormatting sqref="A23">
+    <cfRule type="expression" dxfId="18" priority="10">
+      <formula>MAX($B$2:$B$18)=$B23</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="11">
+      <formula>$D23=$F$2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A24">
+    <cfRule type="expression" dxfId="16" priority="12">
+      <formula>MAX($B$2:$B$18)=$B23</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24">
+    <cfRule type="expression" dxfId="15" priority="17">
+      <formula>$D24=$F$2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="18">
+      <formula>MAX($B$2:$B$18)=$B24</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25">
+    <cfRule type="expression" dxfId="13" priority="8">
+      <formula>$D25=$F$2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="9">
+      <formula>MAX($B$2:$B$18)=$B25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25:A26">
+    <cfRule type="expression" dxfId="11" priority="6">
+      <formula>MAX($B$2:$B$18)=$B25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="expression" dxfId="10" priority="5">
+      <formula>$D26=$F$2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26:A27">
+    <cfRule type="expression" dxfId="9" priority="3">
+      <formula>MAX($B$2:$B$18)=$B26</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>MAX($B$2:$B$18)=$B27</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>$D27=$F$2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:E18">
+    <cfRule type="expression" dxfId="6" priority="28">
+      <formula>$D2=$F$2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="29">
+      <formula>MAX($B$2:$B$18)=$B2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B18">
+    <cfRule type="expression" dxfId="4" priority="25">
       <formula>MAX($B$2:$B$18)=$B2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D18">
-    <cfRule type="expression" dxfId="26" priority="27">
-      <formula>MAX($B$2:$B$18)=$B2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:E18">
-    <cfRule type="expression" dxfId="25" priority="28">
-      <formula>$D2=$F$2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:E18">
-    <cfRule type="expression" dxfId="24" priority="29">
+    <cfRule type="expression" dxfId="3" priority="27">
       <formula>MAX($B$2:$B$18)=$B2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F18">
-    <cfRule type="expression" dxfId="23" priority="22">
+    <cfRule type="expression" dxfId="2" priority="22">
       <formula>MAX($B$2:$B$18)=$B2</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
-    <cfRule type="expression" dxfId="22" priority="23">
+    <cfRule type="expression" dxfId="1" priority="23">
       <formula>$D2=$F$2</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
-    <cfRule type="expression" dxfId="21" priority="24">
+    <cfRule type="expression" dxfId="0" priority="24">
       <formula>MAX($B$2:$B$18)=$B2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
-    <cfRule type="expression" dxfId="17" priority="16">
-      <formula>MAX($B$2:$B$18)=$B24</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
-    <cfRule type="expression" dxfId="16" priority="17">
-      <formula>$D24=$F$2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
-    <cfRule type="expression" dxfId="15" priority="18">
-      <formula>MAX($B$2:$B$18)=$B24</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="expression" dxfId="11" priority="10">
-      <formula>MAX($B$2:$B$18)=$B23</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>$D23=$F$2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="expression" dxfId="9" priority="12">
-      <formula>MAX($B$2:$B$18)=$B23</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
-    <cfRule type="expression" dxfId="8" priority="7">
-      <formula>MAX($B$2:$B$18)=$B25</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$D25=$F$2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
-    <cfRule type="expression" dxfId="6" priority="9">
-      <formula>MAX($B$2:$B$18)=$B25</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="expression" dxfId="5" priority="4">
-      <formula>MAX($B$2:$B$18)=$B26</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>$D26=$F$2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="expression" dxfId="3" priority="6">
-      <formula>MAX($B$2:$B$18)=$B26</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>MAX($B$2:$B$18)=$B27</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$D27=$F$2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>MAX($B$2:$B$18)=$B27</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -3071,13 +2991,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="2" max="18" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3133,7 +3053,7 @@
         <v>5600017</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3189,7 +3109,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -3245,7 +3165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -3301,7 +3221,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3357,7 +3277,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -3366,7 +3286,7 @@
         <v>5600004</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -3375,7 +3295,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -3384,7 +3304,7 @@
         <v>CD</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -3393,7 +3313,7 @@
         <v>Central</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -3411,7 +3331,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="15.625" customWidth="1"/>
@@ -3422,7 +3342,7 @@
     <col min="7" max="11" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" customHeight="1">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
@@ -3447,7 +3367,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="14.25" customHeight="1">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -3470,7 +3390,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -3493,7 +3413,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -3516,7 +3436,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -3539,7 +3459,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="14.25" customHeight="1">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -3562,7 +3482,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -3581,7 +3501,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="14.25" customHeight="1">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -3600,7 +3520,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -3619,7 +3539,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -3632,7 +3552,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -3645,7 +3565,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -3658,7 +3578,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -3671,7 +3591,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="14.25" customHeight="1">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -3684,7 +3604,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" ht="14.25" customHeight="1">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -3697,7 +3617,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="14.25" customHeight="1">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>14</v>
       </c>
@@ -3718,7 +3638,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" ht="14.25" customHeight="1">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>1</v>
       </c>
@@ -3749,7 +3669,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.25" customHeight="1">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>2</v>
       </c>
@@ -3780,7 +3700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.25" customHeight="1">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>3</v>
       </c>
@@ -3799,7 +3719,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" ht="14.25" customHeight="1">
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>4</v>
       </c>
@@ -3818,7 +3738,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" ht="14.25" customHeight="1">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>5</v>
       </c>
@@ -3837,7 +3757,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" ht="14.25" customHeight="1">
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>6</v>
       </c>
@@ -3856,7 +3776,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" ht="14.25" customHeight="1">
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>7</v>
       </c>
@@ -3875,7 +3795,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" ht="14.25" customHeight="1">
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>8</v>
       </c>
@@ -3894,7 +3814,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="14.25" customHeight="1">
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3907,7 +3827,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" ht="14.25" customHeight="1">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3920,7 +3840,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" ht="14.25" customHeight="1">
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3933,7 +3853,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" ht="14.25" customHeight="1">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3946,7 +3866,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" ht="14.25" customHeight="1">
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3959,7 +3879,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3972,7 +3892,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" ht="14.25" customHeight="1">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3985,7 +3905,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11" ht="14.25" customHeight="1">
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3998,7 +3918,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>14</v>
       </c>
@@ -4021,7 +3941,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1">
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>1</v>
       </c>
@@ -4042,7 +3962,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1">
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>2</v>
       </c>
@@ -4063,7 +3983,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1">
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>3</v>
       </c>
@@ -4084,7 +4004,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1">
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>4</v>
       </c>
@@ -4105,7 +4025,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" ht="14.25" customHeight="1">
+    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>5</v>
       </c>
@@ -4122,7 +4042,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" ht="14.25" customHeight="1">
+    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>6</v>
       </c>
@@ -4139,7 +4059,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" ht="14.25" customHeight="1">
+    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>7</v>
       </c>
@@ -4156,7 +4076,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" ht="14.25" customHeight="1">
+    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>8</v>
       </c>
@@ -4173,7 +4093,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" ht="14.25" customHeight="1">
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>9</v>
       </c>
@@ -4190,7 +4110,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" ht="14.25" customHeight="1">
+    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>10</v>
       </c>
@@ -4207,7 +4127,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" ht="14.25" customHeight="1">
+    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4220,7 +4140,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" ht="14.25" customHeight="1">
+    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4233,7 +4153,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" ht="14.25" customHeight="1">
+    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4246,7 +4166,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" ht="14.25" customHeight="1">
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4259,7 +4179,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11" ht="14.25" customHeight="1">
+    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4272,7 +4192,7 @@
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11" ht="14.25" customHeight="1">
+    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4285,7 +4205,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" ht="14.25" customHeight="1">
+    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -4298,7 +4218,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11" ht="14.25" customHeight="1">
+    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -4311,7 +4231,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11" ht="14.25" customHeight="1">
+    <row r="52" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -4324,7 +4244,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11" ht="14.25" customHeight="1">
+    <row r="53" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -4337,7 +4257,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11" ht="14.25" customHeight="1">
+    <row r="54" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -4350,7 +4270,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11" ht="14.25" customHeight="1">
+    <row r="55" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -4363,7 +4283,7 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:11" ht="14.25" customHeight="1">
+    <row r="56" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -4376,7 +4296,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11" ht="14.25" customHeight="1">
+    <row r="57" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -4389,7 +4309,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11" ht="14.25" customHeight="1">
+    <row r="58" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -4402,7 +4322,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11" ht="14.25" customHeight="1">
+    <row r="59" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -4415,7 +4335,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11" ht="14.25" customHeight="1">
+    <row r="60" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -4428,7 +4348,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11" ht="14.25" customHeight="1">
+    <row r="61" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -4441,7 +4361,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11" ht="14.25" customHeight="1">
+    <row r="62" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -4454,7 +4374,7 @@
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11" ht="14.25" customHeight="1">
+    <row r="63" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -4467,7 +4387,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11" ht="14.25" customHeight="1">
+    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -4480,7 +4400,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11" ht="14.25" customHeight="1">
+    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -4493,7 +4413,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11" ht="14.25" customHeight="1">
+    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -4506,7 +4426,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:11" ht="14.25" customHeight="1">
+    <row r="67" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -4519,7 +4439,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11" ht="14.25" customHeight="1">
+    <row r="68" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -4532,7 +4452,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11" ht="14.25" customHeight="1">
+    <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -4545,7 +4465,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:11" ht="14.25" customHeight="1">
+    <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -4558,7 +4478,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:11" ht="14.25" customHeight="1">
+    <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -4571,7 +4491,7 @@
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="1:11" ht="14.25" customHeight="1">
+    <row r="72" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -4584,7 +4504,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" ht="14.25" customHeight="1">
+    <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -4597,7 +4517,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:11" ht="14.25" customHeight="1">
+    <row r="74" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -4610,7 +4530,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" ht="14.25" customHeight="1">
+    <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -4623,7 +4543,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" ht="14.25" customHeight="1">
+    <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -4636,7 +4556,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:11" ht="14.25" customHeight="1">
+    <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4649,7 +4569,7 @@
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="1:11" ht="14.25" customHeight="1">
+    <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -4662,7 +4582,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1">
+    <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -4675,7 +4595,7 @@
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="1:11" ht="14.25" customHeight="1">
+    <row r="80" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -4688,7 +4608,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11" ht="14.25" customHeight="1">
+    <row r="81" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -4701,7 +4621,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" ht="14.25" customHeight="1">
+    <row r="82" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -4714,7 +4634,7 @@
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
     </row>
-    <row r="83" spans="1:11" ht="14.25" customHeight="1">
+    <row r="83" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -4727,7 +4647,7 @@
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
     </row>
-    <row r="84" spans="1:11" ht="14.25" customHeight="1">
+    <row r="84" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -4740,7 +4660,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
     </row>
-    <row r="85" spans="1:11" ht="14.25" customHeight="1">
+    <row r="85" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -4753,7 +4673,7 @@
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
     </row>
-    <row r="86" spans="1:11" ht="14.25" customHeight="1">
+    <row r="86" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4766,7 +4686,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="1:11" ht="14.25" customHeight="1">
+    <row r="87" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4779,7 +4699,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
     </row>
-    <row r="88" spans="1:11" ht="14.25" customHeight="1">
+    <row r="88" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -4792,7 +4712,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
     </row>
-    <row r="89" spans="1:11" ht="14.25" customHeight="1">
+    <row r="89" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -4805,7 +4725,7 @@
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
     </row>
-    <row r="90" spans="1:11" ht="14.25" customHeight="1">
+    <row r="90" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -4818,7 +4738,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
     </row>
-    <row r="91" spans="1:11" ht="14.25" customHeight="1">
+    <row r="91" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -4831,7 +4751,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
     </row>
-    <row r="92" spans="1:11" ht="14.25" customHeight="1">
+    <row r="92" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -4844,7 +4764,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
     </row>
-    <row r="93" spans="1:11" ht="14.25" customHeight="1">
+    <row r="93" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -4857,7 +4777,7 @@
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
     </row>
-    <row r="94" spans="1:11" ht="14.25" customHeight="1">
+    <row r="94" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -4870,7 +4790,7 @@
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
     </row>
-    <row r="95" spans="1:11" ht="14.25" customHeight="1">
+    <row r="95" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -4883,7 +4803,7 @@
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
     </row>
-    <row r="96" spans="1:11" ht="14.25" customHeight="1">
+    <row r="96" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -4896,7 +4816,7 @@
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
     </row>
-    <row r="97" spans="1:11" ht="14.25" customHeight="1">
+    <row r="97" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -4909,7 +4829,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
     </row>
-    <row r="98" spans="1:11" ht="14.25" customHeight="1">
+    <row r="98" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -4922,7 +4842,7 @@
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
     </row>
-    <row r="99" spans="1:11" ht="14.25" customHeight="1">
+    <row r="99" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4935,7 +4855,7 @@
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
     </row>
-    <row r="100" spans="1:11" ht="14.25" customHeight="1">
+    <row r="100" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4957,7 +4877,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L100"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -4971,7 +4891,7 @@
     <col min="12" max="12" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.25" customHeight="1">
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4985,7 +4905,7 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="14.25" customHeight="1">
+    <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>35</v>
       </c>
@@ -5001,7 +4921,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="14.25" customHeight="1">
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -5015,7 +4935,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="14.25" customHeight="1">
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>36</v>
       </c>
@@ -5043,7 +4963,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="14.25" customHeight="1">
+    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>43</v>
       </c>
@@ -5075,7 +4995,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="19"/>
     </row>
-    <row r="6" spans="1:12" ht="14.25" customHeight="1">
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>42</v>
       </c>
@@ -5107,7 +5027,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="19"/>
     </row>
-    <row r="7" spans="1:12" ht="14.25" customHeight="1">
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>44</v>
       </c>
@@ -5139,7 +5059,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" spans="1:12" ht="14.25" customHeight="1">
+    <row r="8" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>45</v>
       </c>
@@ -5171,7 +5091,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" spans="1:12" ht="14.25" customHeight="1">
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>46</v>
       </c>
@@ -5198,7 +5118,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="14.25" customHeight="1">
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -5212,7 +5132,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" ht="14.25" customHeight="1">
+    <row r="11" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -5226,7 +5146,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -5240,7 +5160,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="14.25" customHeight="1">
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>47</v>
       </c>
@@ -5268,7 +5188,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:12" ht="14.25" customHeight="1">
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>50</v>
       </c>
@@ -5300,7 +5220,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:12" ht="14.25" customHeight="1">
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>51</v>
       </c>
@@ -5332,7 +5252,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="14.25" customHeight="1">
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>49</v>
       </c>
@@ -5364,7 +5284,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" ht="14.25" customHeight="1">
+    <row r="17" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>52</v>
       </c>
@@ -5396,7 +5316,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" ht="14.25" customHeight="1">
+    <row r="18" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>53</v>
       </c>
@@ -5423,7 +5343,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" ht="14.25" customHeight="1">
+    <row r="19" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -5437,7 +5357,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" ht="14.25" customHeight="1">
+    <row r="20" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -5451,7 +5371,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="14.25" customHeight="1">
+    <row r="21" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="26" t="s">
         <v>54</v>
       </c>
@@ -5467,7 +5387,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" ht="14.25" customHeight="1">
+    <row r="22" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -5481,7 +5401,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="1:12" ht="14.25" customHeight="1">
+    <row r="23" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>36</v>
       </c>
@@ -5509,7 +5429,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" ht="14.25" customHeight="1">
+    <row r="24" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>43</v>
       </c>
@@ -5541,7 +5461,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" ht="14.25" customHeight="1">
+    <row r="25" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>42</v>
       </c>
@@ -5573,7 +5493,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:12" ht="14.25" customHeight="1">
+    <row r="26" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>44</v>
       </c>
@@ -5605,7 +5525,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" ht="14.25" customHeight="1">
+    <row r="27" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>45</v>
       </c>
@@ -5637,7 +5557,7 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="1:12" ht="14.25" customHeight="1">
+    <row r="28" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>46</v>
       </c>
@@ -5664,7 +5584,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" ht="14.25" customHeight="1">
+    <row r="29" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -5678,7 +5598,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" ht="14.25" customHeight="1">
+    <row r="30" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -5692,7 +5612,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" ht="14.25" customHeight="1">
+    <row r="31" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -5706,7 +5626,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" ht="14.25" customHeight="1">
+    <row r="32" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>47</v>
       </c>
@@ -5732,7 +5652,7 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" ht="14.25" customHeight="1">
+    <row r="33" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>50</v>
       </c>
@@ -5761,7 +5681,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" ht="14.25" customHeight="1">
+    <row r="34" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>51</v>
       </c>
@@ -5790,7 +5710,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" ht="14.25" customHeight="1">
+    <row r="35" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>49</v>
       </c>
@@ -5819,7 +5739,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="1:12" ht="14.25" customHeight="1">
+    <row r="36" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>52</v>
       </c>
@@ -5848,7 +5768,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="1:12" ht="14.25" customHeight="1">
+    <row r="37" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>53</v>
       </c>
@@ -5875,7 +5795,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="1:12" ht="14.25" customHeight="1">
+    <row r="38" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -5889,7 +5809,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="1:12" ht="14.25" customHeight="1">
+    <row r="39" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -5903,7 +5823,7 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="1:12" ht="14.25" customHeight="1">
+    <row r="40" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -5917,7 +5837,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="1:12" ht="14.25" customHeight="1">
+    <row r="41" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>56</v>
       </c>
@@ -5933,7 +5853,7 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="1:12" ht="14.25" customHeight="1">
+    <row r="42" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -5947,7 +5867,7 @@
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="1:12" ht="14.25" customHeight="1">
+    <row r="43" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
         <v>36</v>
       </c>
@@ -5977,7 +5897,7 @@
       <c r="K43" s="21"/>
       <c r="L43" s="21"/>
     </row>
-    <row r="44" spans="1:12" ht="14.25" customHeight="1">
+    <row r="44" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>43</v>
       </c>
@@ -6011,7 +5931,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="1:12" ht="14.25" customHeight="1">
+    <row r="45" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>42</v>
       </c>
@@ -6045,7 +5965,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" spans="1:12" ht="14.25" customHeight="1">
+    <row r="46" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>44</v>
       </c>
@@ -6079,7 +5999,7 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" spans="1:12" ht="14.25" customHeight="1">
+    <row r="47" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>45</v>
       </c>
@@ -6113,7 +6033,7 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="1:12" ht="14.25" customHeight="1">
+    <row r="48" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>46</v>
       </c>
@@ -6142,7 +6062,7 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" spans="1:12" ht="14.25" customHeight="1">
+    <row r="49" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -6156,7 +6076,7 @@
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
     </row>
-    <row r="50" spans="1:12" ht="14.25" customHeight="1">
+    <row r="50" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -6170,7 +6090,7 @@
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
     </row>
-    <row r="51" spans="1:12" ht="14.25" customHeight="1">
+    <row r="51" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -6184,7 +6104,7 @@
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
     </row>
-    <row r="52" spans="1:12" ht="14.25" customHeight="1">
+    <row r="52" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -6198,7 +6118,7 @@
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
     </row>
-    <row r="53" spans="1:12" ht="14.25" customHeight="1">
+    <row r="53" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -6212,7 +6132,7 @@
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
     </row>
-    <row r="54" spans="1:12" ht="14.25" customHeight="1">
+    <row r="54" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -6226,7 +6146,7 @@
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
     </row>
-    <row r="55" spans="1:12" ht="14.25" customHeight="1">
+    <row r="55" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -6240,7 +6160,7 @@
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
-    <row r="56" spans="1:12" ht="14.25" customHeight="1">
+    <row r="56" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -6254,7 +6174,7 @@
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
-    <row r="57" spans="1:12" ht="14.25" customHeight="1">
+    <row r="57" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -6268,7 +6188,7 @@
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
     </row>
-    <row r="58" spans="1:12" ht="14.25" customHeight="1">
+    <row r="58" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -6282,7 +6202,7 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="1:12" ht="14.25" customHeight="1">
+    <row r="59" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -6296,7 +6216,7 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="1:12" ht="14.25" customHeight="1">
+    <row r="60" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -6310,7 +6230,7 @@
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
     </row>
-    <row r="61" spans="1:12" ht="14.25" customHeight="1">
+    <row r="61" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -6324,7 +6244,7 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="1:12" ht="14.25" customHeight="1">
+    <row r="62" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -6338,7 +6258,7 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="1:12" ht="14.25" customHeight="1">
+    <row r="63" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -6352,7 +6272,7 @@
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
     </row>
-    <row r="64" spans="1:12" ht="14.25" customHeight="1">
+    <row r="64" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -6366,7 +6286,7 @@
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
     </row>
-    <row r="65" spans="1:12" ht="14.25" customHeight="1">
+    <row r="65" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -6380,7 +6300,7 @@
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
     </row>
-    <row r="66" spans="1:12" ht="14.25" customHeight="1">
+    <row r="66" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -6394,7 +6314,7 @@
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
     </row>
-    <row r="67" spans="1:12" ht="14.25" customHeight="1">
+    <row r="67" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -6408,7 +6328,7 @@
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
     </row>
-    <row r="68" spans="1:12" ht="14.25" customHeight="1">
+    <row r="68" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -6422,7 +6342,7 @@
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
     </row>
-    <row r="69" spans="1:12" ht="14.25" customHeight="1">
+    <row r="69" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -6436,7 +6356,7 @@
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" spans="1:12" ht="14.25" customHeight="1">
+    <row r="70" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -6450,7 +6370,7 @@
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
     </row>
-    <row r="71" spans="1:12" ht="14.25" customHeight="1">
+    <row r="71" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -6464,7 +6384,7 @@
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
     </row>
-    <row r="72" spans="1:12" ht="14.25" customHeight="1">
+    <row r="72" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -6478,7 +6398,7 @@
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
     </row>
-    <row r="73" spans="1:12" ht="14.25" customHeight="1">
+    <row r="73" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -6492,7 +6412,7 @@
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
     </row>
-    <row r="74" spans="1:12" ht="14.25" customHeight="1">
+    <row r="74" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -6506,7 +6426,7 @@
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
     </row>
-    <row r="75" spans="1:12" ht="14.25" customHeight="1">
+    <row r="75" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -6520,7 +6440,7 @@
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
     </row>
-    <row r="76" spans="1:12" ht="14.25" customHeight="1">
+    <row r="76" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -6534,7 +6454,7 @@
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" spans="1:12" ht="14.25" customHeight="1">
+    <row r="77" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -6548,7 +6468,7 @@
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
     </row>
-    <row r="78" spans="1:12" ht="14.25" customHeight="1">
+    <row r="78" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -6562,7 +6482,7 @@
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
     </row>
-    <row r="79" spans="1:12" ht="14.25" customHeight="1">
+    <row r="79" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -6576,7 +6496,7 @@
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
     </row>
-    <row r="80" spans="1:12" ht="14.25" customHeight="1">
+    <row r="80" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -6590,7 +6510,7 @@
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
     </row>
-    <row r="81" spans="1:12" ht="14.25" customHeight="1">
+    <row r="81" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -6604,7 +6524,7 @@
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
     </row>
-    <row r="82" spans="1:12" ht="14.25" customHeight="1">
+    <row r="82" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -6618,7 +6538,7 @@
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
     </row>
-    <row r="83" spans="1:12" ht="14.25" customHeight="1">
+    <row r="83" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -6632,7 +6552,7 @@
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
     </row>
-    <row r="84" spans="1:12" ht="14.25" customHeight="1">
+    <row r="84" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -6646,7 +6566,7 @@
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
     </row>
-    <row r="85" spans="1:12" ht="14.25" customHeight="1">
+    <row r="85" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -6660,7 +6580,7 @@
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
     </row>
-    <row r="86" spans="1:12" ht="14.25" customHeight="1">
+    <row r="86" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -6674,7 +6594,7 @@
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
     </row>
-    <row r="87" spans="1:12" ht="14.25" customHeight="1">
+    <row r="87" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -6688,7 +6608,7 @@
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
     </row>
-    <row r="88" spans="1:12" ht="14.25" customHeight="1">
+    <row r="88" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -6702,7 +6622,7 @@
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
     </row>
-    <row r="89" spans="1:12" ht="14.25" customHeight="1">
+    <row r="89" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -6716,7 +6636,7 @@
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
     </row>
-    <row r="90" spans="1:12" ht="14.25" customHeight="1">
+    <row r="90" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -6730,7 +6650,7 @@
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
     </row>
-    <row r="91" spans="1:12" ht="14.25" customHeight="1">
+    <row r="91" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -6744,7 +6664,7 @@
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
     </row>
-    <row r="92" spans="1:12" ht="14.25" customHeight="1">
+    <row r="92" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -6758,7 +6678,7 @@
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
     </row>
-    <row r="93" spans="1:12" ht="14.25" customHeight="1">
+    <row r="93" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -6772,7 +6692,7 @@
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
     </row>
-    <row r="94" spans="1:12" ht="14.25" customHeight="1">
+    <row r="94" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -6786,7 +6706,7 @@
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
     </row>
-    <row r="95" spans="1:12" ht="14.25" customHeight="1">
+    <row r="95" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -6800,7 +6720,7 @@
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
     </row>
-    <row r="96" spans="1:12" ht="14.25" customHeight="1">
+    <row r="96" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -6814,7 +6734,7 @@
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
     </row>
-    <row r="97" spans="1:12" ht="14.25" customHeight="1">
+    <row r="97" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -6828,7 +6748,7 @@
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
     </row>
-    <row r="98" spans="1:12" ht="14.25" customHeight="1">
+    <row r="98" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -6842,7 +6762,7 @@
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
     </row>
-    <row r="99" spans="1:12" ht="14.25" customHeight="1">
+    <row r="99" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -6856,7 +6776,7 @@
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
     </row>
-    <row r="100" spans="1:12" ht="14.25" customHeight="1">
+    <row r="100" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -6892,7 +6812,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7.875" customWidth="1"/>
     <col min="3" max="3" width="11.75" customWidth="1"/>
@@ -6904,7 +6824,7 @@
     <col min="9" max="11" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" customHeight="1">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>58</v>
       </c>
@@ -6925,7 +6845,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="14.25" customHeight="1">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1001</v>
       </c>
@@ -6947,7 +6867,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1002</v>
       </c>
@@ -6964,7 +6884,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1003</v>
       </c>
@@ -6981,7 +6901,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>1004</v>
       </c>
@@ -6998,7 +6918,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="14.25" customHeight="1">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>1005</v>
       </c>
@@ -7015,7 +6935,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -7028,7 +6948,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="14.25" customHeight="1">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -7041,7 +6961,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>59</v>
       </c>
@@ -7064,7 +6984,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>61</v>
       </c>
@@ -7088,7 +7008,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
@@ -7112,7 +7032,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>63</v>
       </c>
@@ -7131,7 +7051,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>64</v>
       </c>
@@ -7150,7 +7070,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="14.25" customHeight="1">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>65</v>
       </c>
@@ -7169,7 +7089,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" ht="14.25" customHeight="1">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -7182,7 +7102,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="14.25" customHeight="1">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -7195,7 +7115,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" ht="14.25" customHeight="1">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -7208,7 +7128,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" ht="14.25" customHeight="1">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>59</v>
       </c>
@@ -7235,7 +7155,7 @@
       </c>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" ht="14.25" customHeight="1">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>61</v>
       </c>
@@ -7263,7 +7183,7 @@
       </c>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" ht="14.25" customHeight="1">
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>62</v>
       </c>
@@ -7291,7 +7211,7 @@
       </c>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" ht="14.25" customHeight="1">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>63</v>
       </c>
@@ -7314,7 +7234,7 @@
       </c>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" ht="14.25" customHeight="1">
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>64</v>
       </c>
@@ -7337,7 +7257,7 @@
       </c>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" ht="14.25" customHeight="1">
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>65</v>
       </c>
@@ -7360,7 +7280,7 @@
       </c>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" ht="14.25" customHeight="1">
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -7373,7 +7293,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="14.25" customHeight="1">
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -7386,7 +7306,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" ht="14.25" customHeight="1">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -7399,7 +7319,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" ht="14.25" customHeight="1">
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -7412,7 +7332,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" ht="14.25" customHeight="1">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -7425,7 +7345,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" ht="14.25" customHeight="1">
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -7438,7 +7358,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -7451,7 +7371,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" ht="14.25" customHeight="1">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -7464,7 +7384,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11" ht="14.25" customHeight="1">
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -7477,7 +7397,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -7490,7 +7410,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1">
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -7503,7 +7423,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1">
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -7516,7 +7436,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1">
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -7529,7 +7449,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1">
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -7542,7 +7462,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" ht="14.25" customHeight="1">
+    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -7555,7 +7475,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" ht="14.25" customHeight="1">
+    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -7568,7 +7488,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" ht="14.25" customHeight="1">
+    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -7581,7 +7501,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" ht="14.25" customHeight="1">
+    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -7594,7 +7514,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" ht="14.25" customHeight="1">
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -7607,7 +7527,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" ht="14.25" customHeight="1">
+    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -7620,7 +7540,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" ht="14.25" customHeight="1">
+    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -7633,7 +7553,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" ht="14.25" customHeight="1">
+    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -7646,7 +7566,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" ht="14.25" customHeight="1">
+    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -7659,7 +7579,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" ht="14.25" customHeight="1">
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -7672,7 +7592,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11" ht="14.25" customHeight="1">
+    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -7685,7 +7605,7 @@
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11" ht="14.25" customHeight="1">
+    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -7698,7 +7618,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" ht="14.25" customHeight="1">
+    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -7711,7 +7631,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11" ht="14.25" customHeight="1">
+    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -7724,7 +7644,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11" ht="14.25" customHeight="1">
+    <row r="52" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -7737,7 +7657,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11" ht="14.25" customHeight="1">
+    <row r="53" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -7750,7 +7670,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11" ht="14.25" customHeight="1">
+    <row r="54" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -7763,7 +7683,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11" ht="14.25" customHeight="1">
+    <row r="55" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -7776,7 +7696,7 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:11" ht="14.25" customHeight="1">
+    <row r="56" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -7789,7 +7709,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11" ht="14.25" customHeight="1">
+    <row r="57" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -7802,7 +7722,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11" ht="14.25" customHeight="1">
+    <row r="58" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -7815,7 +7735,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11" ht="14.25" customHeight="1">
+    <row r="59" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -7828,7 +7748,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11" ht="14.25" customHeight="1">
+    <row r="60" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -7841,7 +7761,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11" ht="14.25" customHeight="1">
+    <row r="61" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -7854,7 +7774,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11" ht="14.25" customHeight="1">
+    <row r="62" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -7867,7 +7787,7 @@
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11" ht="14.25" customHeight="1">
+    <row r="63" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -7880,7 +7800,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11" ht="14.25" customHeight="1">
+    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -7893,7 +7813,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11" ht="14.25" customHeight="1">
+    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -7906,7 +7826,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11" ht="14.25" customHeight="1">
+    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -7919,7 +7839,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:11" ht="14.25" customHeight="1">
+    <row r="67" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -7932,7 +7852,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11" ht="14.25" customHeight="1">
+    <row r="68" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -7945,7 +7865,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11" ht="14.25" customHeight="1">
+    <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -7958,7 +7878,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:11" ht="14.25" customHeight="1">
+    <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -7971,7 +7891,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:11" ht="14.25" customHeight="1">
+    <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -7984,7 +7904,7 @@
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="1:11" ht="14.25" customHeight="1">
+    <row r="72" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -7997,7 +7917,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" ht="14.25" customHeight="1">
+    <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -8010,7 +7930,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:11" ht="14.25" customHeight="1">
+    <row r="74" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -8023,7 +7943,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" ht="14.25" customHeight="1">
+    <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -8036,7 +7956,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" ht="14.25" customHeight="1">
+    <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -8049,7 +7969,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:11" ht="14.25" customHeight="1">
+    <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -8062,7 +7982,7 @@
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="1:11" ht="14.25" customHeight="1">
+    <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -8075,7 +7995,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1">
+    <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -8088,7 +8008,7 @@
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="1:11" ht="14.25" customHeight="1">
+    <row r="80" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -8101,7 +8021,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11" ht="14.25" customHeight="1">
+    <row r="81" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -8114,7 +8034,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" ht="14.25" customHeight="1">
+    <row r="82" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -8127,7 +8047,7 @@
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
     </row>
-    <row r="83" spans="1:11" ht="14.25" customHeight="1">
+    <row r="83" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -8140,7 +8060,7 @@
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
     </row>
-    <row r="84" spans="1:11" ht="14.25" customHeight="1">
+    <row r="84" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -8153,7 +8073,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
     </row>
-    <row r="85" spans="1:11" ht="14.25" customHeight="1">
+    <row r="85" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -8166,7 +8086,7 @@
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
     </row>
-    <row r="86" spans="1:11" ht="14.25" customHeight="1">
+    <row r="86" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -8179,7 +8099,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="1:11" ht="14.25" customHeight="1">
+    <row r="87" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -8192,7 +8112,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
     </row>
-    <row r="88" spans="1:11" ht="14.25" customHeight="1">
+    <row r="88" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -8205,7 +8125,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
     </row>
-    <row r="89" spans="1:11" ht="14.25" customHeight="1">
+    <row r="89" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -8218,7 +8138,7 @@
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
     </row>
-    <row r="90" spans="1:11" ht="14.25" customHeight="1">
+    <row r="90" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -8231,7 +8151,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
     </row>
-    <row r="91" spans="1:11" ht="14.25" customHeight="1">
+    <row r="91" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -8244,7 +8164,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
     </row>
-    <row r="92" spans="1:11" ht="14.25" customHeight="1">
+    <row r="92" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -8257,7 +8177,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
     </row>
-    <row r="93" spans="1:11" ht="14.25" customHeight="1">
+    <row r="93" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -8270,7 +8190,7 @@
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
     </row>
-    <row r="94" spans="1:11" ht="14.25" customHeight="1">
+    <row r="94" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -8283,7 +8203,7 @@
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
     </row>
-    <row r="95" spans="1:11" ht="14.25" customHeight="1">
+    <row r="95" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -8296,7 +8216,7 @@
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
     </row>
-    <row r="96" spans="1:11" ht="14.25" customHeight="1">
+    <row r="96" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -8309,7 +8229,7 @@
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
     </row>
-    <row r="97" spans="1:11" ht="14.25" customHeight="1">
+    <row r="97" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -8322,7 +8242,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
     </row>
-    <row r="98" spans="1:11" ht="14.25" customHeight="1">
+    <row r="98" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -8335,7 +8255,7 @@
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
     </row>
-    <row r="99" spans="1:11" ht="14.25" customHeight="1">
+    <row r="99" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -8348,7 +8268,7 @@
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
     </row>
-    <row r="100" spans="1:11" ht="14.25" customHeight="1">
+    <row r="100" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -8370,7 +8290,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M100"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="9.375" customWidth="1"/>
@@ -8386,7 +8306,7 @@
     <col min="13" max="13" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.25" customHeight="1">
+    <row r="1" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
@@ -8423,7 +8343,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="14.25" customHeight="1">
+    <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -8468,7 +8388,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="14.25" customHeight="1">
+    <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -8513,7 +8433,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="14.25" customHeight="1">
+    <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -8558,7 +8478,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="14.25" customHeight="1">
+    <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -8603,7 +8523,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="14.25" customHeight="1">
+    <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -8648,7 +8568,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="14.25" customHeight="1">
+    <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -8693,7 +8613,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="14.25" customHeight="1">
+    <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -8738,7 +8658,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="14.25" customHeight="1">
+    <row r="9" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -8783,7 +8703,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="14.25" customHeight="1">
+    <row r="10" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -8828,7 +8748,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="14.25" customHeight="1">
+    <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -8843,7 +8763,7 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1">
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8858,7 +8778,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="1:13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -8873,7 +8793,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:13" ht="14.25" customHeight="1">
+    <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -8888,7 +8808,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="1:13" ht="14.25" customHeight="1">
+    <row r="15" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -8903,7 +8823,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="1:13" ht="14.25" customHeight="1">
+    <row r="16" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -8918,7 +8838,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
     </row>
-    <row r="17" spans="1:13" ht="14.25" customHeight="1">
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -8933,7 +8853,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="1:13" ht="14.25" customHeight="1">
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -8948,7 +8868,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="1:13" ht="14.25" customHeight="1">
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -8963,7 +8883,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="1:13" ht="14.25" customHeight="1">
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -8978,7 +8898,7 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="1:13" ht="14.25" customHeight="1">
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -8993,7 +8913,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="1:13" ht="14.25" customHeight="1">
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -9008,7 +8928,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="1:13" ht="14.25" customHeight="1">
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -9023,7 +8943,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="1:13" ht="14.25" customHeight="1">
+    <row r="24" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -9038,7 +8958,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="1:13" ht="14.25" customHeight="1">
+    <row r="25" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -9053,7 +8973,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="1:13" ht="14.25" customHeight="1">
+    <row r="26" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -9068,7 +8988,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="1:13" ht="14.25" customHeight="1">
+    <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -9083,7 +9003,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="1:13" ht="14.25" customHeight="1">
+    <row r="28" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -9098,7 +9018,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="1:13" ht="14.25" customHeight="1">
+    <row r="29" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -9113,7 +9033,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="1:13" ht="14.25" customHeight="1">
+    <row r="30" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -9128,7 +9048,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="1:13" ht="14.25" customHeight="1">
+    <row r="31" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -9143,7 +9063,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="1:13" ht="14.25" customHeight="1">
+    <row r="32" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -9158,7 +9078,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="1:13" ht="14.25" customHeight="1">
+    <row r="33" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -9173,7 +9093,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="1:13" ht="14.25" customHeight="1">
+    <row r="34" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -9188,7 +9108,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="1:13" ht="14.25" customHeight="1">
+    <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -9203,7 +9123,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="1:13" ht="14.25" customHeight="1">
+    <row r="36" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -9218,7 +9138,7 @@
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="1:13" ht="14.25" customHeight="1">
+    <row r="37" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -9233,7 +9153,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="1:13" ht="14.25" customHeight="1">
+    <row r="38" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -9248,7 +9168,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="1:13" ht="14.25" customHeight="1">
+    <row r="39" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -9263,7 +9183,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="1:13" ht="14.25" customHeight="1">
+    <row r="40" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -9278,7 +9198,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="1:13" ht="14.25" customHeight="1">
+    <row r="41" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -9293,7 +9213,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="1:13" ht="14.25" customHeight="1">
+    <row r="42" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -9308,7 +9228,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="1:13" ht="14.25" customHeight="1">
+    <row r="43" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -9323,7 +9243,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="1:13" ht="14.25" customHeight="1">
+    <row r="44" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -9338,7 +9258,7 @@
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="1:13" ht="14.25" customHeight="1">
+    <row r="45" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -9353,7 +9273,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="1:13" ht="14.25" customHeight="1">
+    <row r="46" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -9368,7 +9288,7 @@
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
     </row>
-    <row r="47" spans="1:13" ht="14.25" customHeight="1">
+    <row r="47" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -9383,7 +9303,7 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="1:13" ht="14.25" customHeight="1">
+    <row r="48" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -9398,7 +9318,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
     </row>
-    <row r="49" spans="1:13" ht="14.25" customHeight="1">
+    <row r="49" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -9413,7 +9333,7 @@
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="1:13" ht="14.25" customHeight="1">
+    <row r="50" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -9428,7 +9348,7 @@
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
     </row>
-    <row r="51" spans="1:13" ht="14.25" customHeight="1">
+    <row r="51" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -9443,7 +9363,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" spans="1:13" ht="14.25" customHeight="1">
+    <row r="52" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -9458,7 +9378,7 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="1:13" ht="14.25" customHeight="1">
+    <row r="53" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -9473,7 +9393,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="1:13" ht="14.25" customHeight="1">
+    <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -9488,7 +9408,7 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="1:13" ht="14.25" customHeight="1">
+    <row r="55" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -9503,7 +9423,7 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="1:13" ht="14.25" customHeight="1">
+    <row r="56" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -9518,7 +9438,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="1:13" ht="14.25" customHeight="1">
+    <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -9533,7 +9453,7 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="1:13" ht="14.25" customHeight="1">
+    <row r="58" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -9548,7 +9468,7 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="1:13" ht="14.25" customHeight="1">
+    <row r="59" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -9563,7 +9483,7 @@
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="1:13" ht="14.25" customHeight="1">
+    <row r="60" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -9578,7 +9498,7 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="1:13" ht="14.25" customHeight="1">
+    <row r="61" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -9593,7 +9513,7 @@
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="1:13" ht="14.25" customHeight="1">
+    <row r="62" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -9608,7 +9528,7 @@
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
     </row>
-    <row r="63" spans="1:13" ht="14.25" customHeight="1">
+    <row r="63" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -9623,7 +9543,7 @@
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="1:13" ht="14.25" customHeight="1">
+    <row r="64" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -9638,7 +9558,7 @@
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
     </row>
-    <row r="65" spans="1:13" ht="14.25" customHeight="1">
+    <row r="65" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -9653,7 +9573,7 @@
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
     </row>
-    <row r="66" spans="1:13" ht="14.25" customHeight="1">
+    <row r="66" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -9668,7 +9588,7 @@
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
     </row>
-    <row r="67" spans="1:13" ht="14.25" customHeight="1">
+    <row r="67" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -9683,7 +9603,7 @@
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
     </row>
-    <row r="68" spans="1:13" ht="14.25" customHeight="1">
+    <row r="68" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -9698,7 +9618,7 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
     </row>
-    <row r="69" spans="1:13" ht="14.25" customHeight="1">
+    <row r="69" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -9713,7 +9633,7 @@
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
     </row>
-    <row r="70" spans="1:13" ht="14.25" customHeight="1">
+    <row r="70" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -9728,7 +9648,7 @@
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
     </row>
-    <row r="71" spans="1:13" ht="14.25" customHeight="1">
+    <row r="71" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -9743,7 +9663,7 @@
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
     </row>
-    <row r="72" spans="1:13" ht="14.25" customHeight="1">
+    <row r="72" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -9758,7 +9678,7 @@
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
     </row>
-    <row r="73" spans="1:13" ht="14.25" customHeight="1">
+    <row r="73" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -9773,7 +9693,7 @@
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
     </row>
-    <row r="74" spans="1:13" ht="14.25" customHeight="1">
+    <row r="74" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -9788,7 +9708,7 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
     </row>
-    <row r="75" spans="1:13" ht="14.25" customHeight="1">
+    <row r="75" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -9803,7 +9723,7 @@
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
     </row>
-    <row r="76" spans="1:13" ht="14.25" customHeight="1">
+    <row r="76" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -9818,7 +9738,7 @@
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
     </row>
-    <row r="77" spans="1:13" ht="14.25" customHeight="1">
+    <row r="77" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -9833,7 +9753,7 @@
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
     </row>
-    <row r="78" spans="1:13" ht="14.25" customHeight="1">
+    <row r="78" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -9848,7 +9768,7 @@
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
     </row>
-    <row r="79" spans="1:13" ht="14.25" customHeight="1">
+    <row r="79" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -9863,7 +9783,7 @@
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
     </row>
-    <row r="80" spans="1:13" ht="14.25" customHeight="1">
+    <row r="80" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -9878,7 +9798,7 @@
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
     </row>
-    <row r="81" spans="1:13" ht="14.25" customHeight="1">
+    <row r="81" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -9893,7 +9813,7 @@
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
     </row>
-    <row r="82" spans="1:13" ht="14.25" customHeight="1">
+    <row r="82" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -9908,7 +9828,7 @@
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" spans="1:13" ht="14.25" customHeight="1">
+    <row r="83" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -9923,7 +9843,7 @@
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
     </row>
-    <row r="84" spans="1:13" ht="14.25" customHeight="1">
+    <row r="84" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -9938,7 +9858,7 @@
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="1:13" ht="14.25" customHeight="1">
+    <row r="85" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -9953,7 +9873,7 @@
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="1:13" ht="14.25" customHeight="1">
+    <row r="86" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -9968,7 +9888,7 @@
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="1:13" ht="14.25" customHeight="1">
+    <row r="87" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -9983,7 +9903,7 @@
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
     </row>
-    <row r="88" spans="1:13" ht="14.25" customHeight="1">
+    <row r="88" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -9998,7 +9918,7 @@
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
     </row>
-    <row r="89" spans="1:13" ht="14.25" customHeight="1">
+    <row r="89" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -10013,7 +9933,7 @@
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
     </row>
-    <row r="90" spans="1:13" ht="14.25" customHeight="1">
+    <row r="90" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -10028,7 +9948,7 @@
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
     </row>
-    <row r="91" spans="1:13" ht="14.25" customHeight="1">
+    <row r="91" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -10043,7 +9963,7 @@
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
     </row>
-    <row r="92" spans="1:13" ht="14.25" customHeight="1">
+    <row r="92" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -10058,7 +9978,7 @@
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
     </row>
-    <row r="93" spans="1:13" ht="14.25" customHeight="1">
+    <row r="93" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -10073,7 +9993,7 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
     </row>
-    <row r="94" spans="1:13" ht="14.25" customHeight="1">
+    <row r="94" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -10088,7 +10008,7 @@
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
     </row>
-    <row r="95" spans="1:13" ht="14.25" customHeight="1">
+    <row r="95" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -10103,7 +10023,7 @@
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
     </row>
-    <row r="96" spans="1:13" ht="14.25" customHeight="1">
+    <row r="96" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -10118,7 +10038,7 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
     </row>
-    <row r="97" spans="1:13" ht="14.25" customHeight="1">
+    <row r="97" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -10133,7 +10053,7 @@
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
     </row>
-    <row r="98" spans="1:13" ht="14.25" customHeight="1">
+    <row r="98" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -10148,7 +10068,7 @@
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
     </row>
-    <row r="99" spans="1:13" ht="14.25" customHeight="1">
+    <row r="99" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -10163,7 +10083,7 @@
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
     </row>
-    <row r="100" spans="1:13" ht="14.25" customHeight="1">
+    <row r="100" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -10187,7 +10107,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10195,7 +10115,7 @@
     <col min="4" max="11" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" customHeight="1">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
@@ -10214,7 +10134,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="14.25" customHeight="1">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -10233,7 +10153,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -10250,7 +10170,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -10267,7 +10187,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -10287,7 +10207,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="14.25" customHeight="1">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -10306,7 +10226,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -10323,7 +10243,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="14.25" customHeight="1">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -10342,7 +10262,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -10361,7 +10281,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -10380,7 +10300,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -10399,7 +10319,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -10418,7 +10338,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -10435,7 +10355,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="14.25" customHeight="1">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -10454,7 +10374,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" ht="14.25" customHeight="1">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -10471,7 +10391,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="14.25" customHeight="1">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -10488,7 +10408,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" ht="14.25" customHeight="1">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -10505,7 +10425,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" ht="14.25" customHeight="1">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -10524,7 +10444,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" ht="14.25" customHeight="1">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -10541,7 +10461,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" ht="14.25" customHeight="1">
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -10560,7 +10480,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" ht="14.25" customHeight="1">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -10577,7 +10497,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" ht="14.25" customHeight="1">
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>21</v>
       </c>
@@ -10594,7 +10514,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" ht="14.25" customHeight="1">
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -10611,7 +10531,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" ht="14.25" customHeight="1">
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -10628,7 +10548,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="14.25" customHeight="1">
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -10645,7 +10565,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" ht="14.25" customHeight="1">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -10662,7 +10582,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" ht="14.25" customHeight="1">
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -10681,7 +10601,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" ht="14.25" customHeight="1">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>27</v>
       </c>
@@ -10698,7 +10618,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" ht="14.25" customHeight="1">
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -10711,7 +10631,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -10724,7 +10644,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" ht="14.25" customHeight="1">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -10737,7 +10657,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11" ht="14.25" customHeight="1">
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -10750,7 +10670,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -10763,7 +10683,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1">
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -10776,7 +10696,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1">
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -10789,7 +10709,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1">
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -10802,7 +10722,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1">
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -10815,7 +10735,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" ht="14.25" customHeight="1">
+    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -10828,7 +10748,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" ht="14.25" customHeight="1">
+    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -10841,7 +10761,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" ht="14.25" customHeight="1">
+    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -10854,7 +10774,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" ht="14.25" customHeight="1">
+    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -10867,7 +10787,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" ht="14.25" customHeight="1">
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -10880,7 +10800,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" ht="14.25" customHeight="1">
+    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -10893,7 +10813,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" ht="14.25" customHeight="1">
+    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -10906,7 +10826,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" ht="14.25" customHeight="1">
+    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -10919,7 +10839,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" ht="14.25" customHeight="1">
+    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -10932,7 +10852,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" ht="14.25" customHeight="1">
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -10945,7 +10865,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11" ht="14.25" customHeight="1">
+    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -10958,7 +10878,7 @@
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11" ht="14.25" customHeight="1">
+    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -10971,7 +10891,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" ht="14.25" customHeight="1">
+    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -10984,7 +10904,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11" ht="14.25" customHeight="1">
+    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -10997,7 +10917,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11" ht="14.25" customHeight="1">
+    <row r="52" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -11010,7 +10930,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11" ht="14.25" customHeight="1">
+    <row r="53" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -11023,7 +10943,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11" ht="14.25" customHeight="1">
+    <row r="54" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -11036,7 +10956,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11" ht="14.25" customHeight="1">
+    <row r="55" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -11049,7 +10969,7 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:11" ht="14.25" customHeight="1">
+    <row r="56" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -11062,7 +10982,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11" ht="14.25" customHeight="1">
+    <row r="57" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -11075,7 +10995,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11" ht="14.25" customHeight="1">
+    <row r="58" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -11088,7 +11008,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11" ht="14.25" customHeight="1">
+    <row r="59" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -11101,7 +11021,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11" ht="14.25" customHeight="1">
+    <row r="60" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -11114,7 +11034,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11" ht="14.25" customHeight="1">
+    <row r="61" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -11127,7 +11047,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11" ht="14.25" customHeight="1">
+    <row r="62" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -11140,7 +11060,7 @@
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11" ht="14.25" customHeight="1">
+    <row r="63" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -11153,7 +11073,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11" ht="14.25" customHeight="1">
+    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -11166,7 +11086,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11" ht="14.25" customHeight="1">
+    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -11179,7 +11099,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11" ht="14.25" customHeight="1">
+    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -11192,7 +11112,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:11" ht="14.25" customHeight="1">
+    <row r="67" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -11205,7 +11125,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11" ht="14.25" customHeight="1">
+    <row r="68" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -11218,7 +11138,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11" ht="14.25" customHeight="1">
+    <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -11231,7 +11151,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:11" ht="14.25" customHeight="1">
+    <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -11244,7 +11164,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:11" ht="14.25" customHeight="1">
+    <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -11257,7 +11177,7 @@
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="1:11" ht="14.25" customHeight="1">
+    <row r="72" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -11270,7 +11190,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" ht="14.25" customHeight="1">
+    <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -11283,7 +11203,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:11" ht="14.25" customHeight="1">
+    <row r="74" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -11296,7 +11216,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" ht="14.25" customHeight="1">
+    <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -11309,7 +11229,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" ht="14.25" customHeight="1">
+    <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -11322,7 +11242,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:11" ht="14.25" customHeight="1">
+    <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -11335,7 +11255,7 @@
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="1:11" ht="14.25" customHeight="1">
+    <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -11348,7 +11268,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1">
+    <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -11361,7 +11281,7 @@
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="1:11" ht="14.25" customHeight="1">
+    <row r="80" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -11374,7 +11294,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11" ht="14.25" customHeight="1">
+    <row r="81" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -11387,7 +11307,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" ht="14.25" customHeight="1">
+    <row r="82" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -11400,7 +11320,7 @@
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
     </row>
-    <row r="83" spans="1:11" ht="14.25" customHeight="1">
+    <row r="83" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -11413,7 +11333,7 @@
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
     </row>
-    <row r="84" spans="1:11" ht="14.25" customHeight="1">
+    <row r="84" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -11426,7 +11346,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
     </row>
-    <row r="85" spans="1:11" ht="14.25" customHeight="1">
+    <row r="85" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -11439,7 +11359,7 @@
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
     </row>
-    <row r="86" spans="1:11" ht="14.25" customHeight="1">
+    <row r="86" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -11452,7 +11372,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="1:11" ht="14.25" customHeight="1">
+    <row r="87" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -11465,7 +11385,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
     </row>
-    <row r="88" spans="1:11" ht="14.25" customHeight="1">
+    <row r="88" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -11478,7 +11398,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
     </row>
-    <row r="89" spans="1:11" ht="14.25" customHeight="1">
+    <row r="89" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -11491,7 +11411,7 @@
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
     </row>
-    <row r="90" spans="1:11" ht="14.25" customHeight="1">
+    <row r="90" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -11504,7 +11424,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
     </row>
-    <row r="91" spans="1:11" ht="14.25" customHeight="1">
+    <row r="91" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -11517,7 +11437,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
     </row>
-    <row r="92" spans="1:11" ht="14.25" customHeight="1">
+    <row r="92" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -11530,7 +11450,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
     </row>
-    <row r="93" spans="1:11" ht="14.25" customHeight="1">
+    <row r="93" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -11543,7 +11463,7 @@
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
     </row>
-    <row r="94" spans="1:11" ht="14.25" customHeight="1">
+    <row r="94" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -11556,7 +11476,7 @@
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
     </row>
-    <row r="95" spans="1:11" ht="14.25" customHeight="1">
+    <row r="95" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -11569,7 +11489,7 @@
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
     </row>
-    <row r="96" spans="1:11" ht="14.25" customHeight="1">
+    <row r="96" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -11582,7 +11502,7 @@
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
     </row>
-    <row r="97" spans="1:11" ht="14.25" customHeight="1">
+    <row r="97" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -11595,7 +11515,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
     </row>
-    <row r="98" spans="1:11" ht="14.25" customHeight="1">
+    <row r="98" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -11608,7 +11528,7 @@
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
     </row>
-    <row r="99" spans="1:11" ht="14.25" customHeight="1">
+    <row r="99" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -11621,7 +11541,7 @@
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
     </row>
-    <row r="100" spans="1:11" ht="14.25" customHeight="1">
+    <row r="100" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -11644,7 +11564,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -11655,7 +11575,7 @@
     <col min="7" max="11" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" customHeight="1">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -11674,7 +11594,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="14.25" customHeight="1">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -11693,7 +11613,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>4</v>
       </c>
@@ -11712,7 +11632,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>16</v>
       </c>
@@ -11731,7 +11651,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -11750,7 +11670,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="14.25" customHeight="1">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>11</v>
       </c>
@@ -11769,7 +11689,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>8</v>
       </c>
@@ -11788,7 +11708,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="14.25" customHeight="1">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -11807,7 +11727,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -11826,7 +11746,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>15</v>
       </c>
@@ -11845,7 +11765,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -11864,7 +11784,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -11883,7 +11803,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>14</v>
       </c>
@@ -11902,7 +11822,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="14.25" customHeight="1">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>6</v>
       </c>
@@ -11921,7 +11841,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" ht="14.25" customHeight="1">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -11940,7 +11860,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="14.25" customHeight="1">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>3</v>
       </c>
@@ -11959,7 +11879,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" ht="14.25" customHeight="1">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -11978,7 +11898,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" ht="14.25" customHeight="1">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -11991,7 +11911,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" ht="14.25" customHeight="1">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -12004,7 +11924,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" ht="14.25" customHeight="1">
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -12017,7 +11937,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" ht="14.25" customHeight="1">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -12030,7 +11950,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" ht="14.25" customHeight="1">
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -12043,7 +11963,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" ht="14.25" customHeight="1">
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -12056,7 +11976,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" ht="14.25" customHeight="1">
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -12069,7 +11989,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="14.25" customHeight="1">
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -12082,7 +12002,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" ht="14.25" customHeight="1">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -12095,7 +12015,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" ht="14.25" customHeight="1">
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -12108,7 +12028,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" ht="14.25" customHeight="1">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -12121,7 +12041,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" ht="14.25" customHeight="1">
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -12134,7 +12054,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -12147,7 +12067,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" ht="14.25" customHeight="1">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -12160,7 +12080,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11" ht="14.25" customHeight="1">
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -12173,7 +12093,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -12186,7 +12106,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1">
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -12199,7 +12119,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1">
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -12212,7 +12132,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1">
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -12225,7 +12145,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1">
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -12238,7 +12158,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" ht="14.25" customHeight="1">
+    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -12251,7 +12171,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" ht="14.25" customHeight="1">
+    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -12264,7 +12184,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" ht="14.25" customHeight="1">
+    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -12277,7 +12197,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" ht="14.25" customHeight="1">
+    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -12290,7 +12210,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" ht="14.25" customHeight="1">
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -12303,7 +12223,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" ht="14.25" customHeight="1">
+    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -12316,7 +12236,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" ht="14.25" customHeight="1">
+    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -12329,7 +12249,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" ht="14.25" customHeight="1">
+    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -12342,7 +12262,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" ht="14.25" customHeight="1">
+    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -12355,7 +12275,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" ht="14.25" customHeight="1">
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -12368,7 +12288,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11" ht="14.25" customHeight="1">
+    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -12381,7 +12301,7 @@
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11" ht="14.25" customHeight="1">
+    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -12394,7 +12314,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" ht="14.25" customHeight="1">
+    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -12407,7 +12327,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11" ht="14.25" customHeight="1">
+    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -12420,7 +12340,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11" ht="14.25" customHeight="1">
+    <row r="52" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -12433,7 +12353,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11" ht="14.25" customHeight="1">
+    <row r="53" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -12446,7 +12366,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11" ht="14.25" customHeight="1">
+    <row r="54" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -12459,7 +12379,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11" ht="14.25" customHeight="1">
+    <row r="55" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -12472,7 +12392,7 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:11" ht="14.25" customHeight="1">
+    <row r="56" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -12485,7 +12405,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11" ht="14.25" customHeight="1">
+    <row r="57" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -12498,7 +12418,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11" ht="14.25" customHeight="1">
+    <row r="58" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -12511,7 +12431,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11" ht="14.25" customHeight="1">
+    <row r="59" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -12524,7 +12444,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11" ht="14.25" customHeight="1">
+    <row r="60" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -12537,7 +12457,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11" ht="14.25" customHeight="1">
+    <row r="61" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -12550,7 +12470,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11" ht="14.25" customHeight="1">
+    <row r="62" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -12563,7 +12483,7 @@
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11" ht="14.25" customHeight="1">
+    <row r="63" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -12576,7 +12496,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11" ht="14.25" customHeight="1">
+    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -12589,7 +12509,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11" ht="14.25" customHeight="1">
+    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -12602,7 +12522,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11" ht="14.25" customHeight="1">
+    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -12615,7 +12535,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:11" ht="14.25" customHeight="1">
+    <row r="67" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -12628,7 +12548,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11" ht="14.25" customHeight="1">
+    <row r="68" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -12641,7 +12561,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11" ht="14.25" customHeight="1">
+    <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -12654,7 +12574,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:11" ht="14.25" customHeight="1">
+    <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -12667,7 +12587,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:11" ht="14.25" customHeight="1">
+    <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -12680,7 +12600,7 @@
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="1:11" ht="14.25" customHeight="1">
+    <row r="72" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -12693,7 +12613,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" ht="14.25" customHeight="1">
+    <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -12706,7 +12626,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:11" ht="14.25" customHeight="1">
+    <row r="74" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -12719,7 +12639,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" ht="14.25" customHeight="1">
+    <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -12732,7 +12652,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" ht="14.25" customHeight="1">
+    <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -12745,7 +12665,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:11" ht="14.25" customHeight="1">
+    <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -12758,7 +12678,7 @@
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="1:11" ht="14.25" customHeight="1">
+    <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -12771,7 +12691,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1">
+    <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -12784,7 +12704,7 @@
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="1:11" ht="14.25" customHeight="1">
+    <row r="80" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -12797,7 +12717,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11" ht="14.25" customHeight="1">
+    <row r="81" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -12810,7 +12730,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" ht="14.25" customHeight="1">
+    <row r="82" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -12823,7 +12743,7 @@
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
     </row>
-    <row r="83" spans="1:11" ht="14.25" customHeight="1">
+    <row r="83" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -12836,7 +12756,7 @@
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
     </row>
-    <row r="84" spans="1:11" ht="14.25" customHeight="1">
+    <row r="84" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -12849,7 +12769,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
     </row>
-    <row r="85" spans="1:11" ht="14.25" customHeight="1">
+    <row r="85" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -12862,7 +12782,7 @@
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
     </row>
-    <row r="86" spans="1:11" ht="14.25" customHeight="1">
+    <row r="86" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -12875,7 +12795,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="1:11" ht="14.25" customHeight="1">
+    <row r="87" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -12888,7 +12808,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
     </row>
-    <row r="88" spans="1:11" ht="14.25" customHeight="1">
+    <row r="88" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -12901,7 +12821,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
     </row>
-    <row r="89" spans="1:11" ht="14.25" customHeight="1">
+    <row r="89" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -12914,7 +12834,7 @@
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
     </row>
-    <row r="90" spans="1:11" ht="14.25" customHeight="1">
+    <row r="90" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -12927,7 +12847,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
     </row>
-    <row r="91" spans="1:11" ht="14.25" customHeight="1">
+    <row r="91" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -12940,7 +12860,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
     </row>
-    <row r="92" spans="1:11" ht="14.25" customHeight="1">
+    <row r="92" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -12953,7 +12873,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
     </row>
-    <row r="93" spans="1:11" ht="14.25" customHeight="1">
+    <row r="93" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -12966,7 +12886,7 @@
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
     </row>
-    <row r="94" spans="1:11" ht="14.25" customHeight="1">
+    <row r="94" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -12979,7 +12899,7 @@
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
     </row>
-    <row r="95" spans="1:11" ht="14.25" customHeight="1">
+    <row r="95" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -12992,7 +12912,7 @@
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
     </row>
-    <row r="96" spans="1:11" ht="14.25" customHeight="1">
+    <row r="96" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -13005,7 +12925,7 @@
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
     </row>
-    <row r="97" spans="1:11" ht="14.25" customHeight="1">
+    <row r="97" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -13018,7 +12938,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
     </row>
-    <row r="98" spans="1:11" ht="14.25" customHeight="1">
+    <row r="98" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -13031,7 +12951,7 @@
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
     </row>
-    <row r="99" spans="1:11" ht="14.25" customHeight="1">
+    <row r="99" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -13044,7 +12964,7 @@
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
     </row>
-    <row r="100" spans="1:11" ht="14.25" customHeight="1">
+    <row r="100" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -13066,7 +12986,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" customWidth="1"/>
     <col min="2" max="2" width="11.125" customWidth="1"/>
@@ -13076,7 +12996,7 @@
     <col min="6" max="11" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" customHeight="1">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
@@ -13100,7 +13020,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="14.25" customHeight="1">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -13124,7 +13044,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -13143,7 +13063,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -13162,7 +13082,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -13181,7 +13101,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="14.25" customHeight="1">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -13200,7 +13120,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -13219,7 +13139,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="14.25" customHeight="1">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -13232,7 +13152,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -13245,7 +13165,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>158</v>
       </c>
@@ -13262,7 +13182,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>159</v>
       </c>
@@ -13279,7 +13199,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -13292,7 +13212,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -13305,7 +13225,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="14.25" customHeight="1">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -13318,7 +13238,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" ht="14.25" customHeight="1">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -13331,7 +13251,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="14.25" customHeight="1">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -13344,7 +13264,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" ht="14.25" customHeight="1">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -13357,7 +13277,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" ht="14.25" customHeight="1">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -13370,7 +13290,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" ht="14.25" customHeight="1">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -13383,7 +13303,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" ht="14.25" customHeight="1">
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -13396,7 +13316,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" ht="14.25" customHeight="1">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -13409,7 +13329,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" ht="14.25" customHeight="1">
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -13422,7 +13342,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" ht="14.25" customHeight="1">
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -13435,7 +13355,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" ht="14.25" customHeight="1">
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -13448,7 +13368,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="14.25" customHeight="1">
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -13461,7 +13381,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" ht="14.25" customHeight="1">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -13474,7 +13394,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" ht="14.25" customHeight="1">
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -13487,7 +13407,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" ht="14.25" customHeight="1">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -13500,7 +13420,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" ht="14.25" customHeight="1">
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -13513,7 +13433,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -13526,7 +13446,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" ht="14.25" customHeight="1">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -13539,7 +13459,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11" ht="14.25" customHeight="1">
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -13552,7 +13472,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -13565,7 +13485,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1">
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -13578,7 +13498,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1">
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -13591,7 +13511,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1">
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -13604,7 +13524,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1">
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -13617,7 +13537,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" ht="14.25" customHeight="1">
+    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -13630,7 +13550,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" ht="14.25" customHeight="1">
+    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -13643,7 +13563,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" ht="14.25" customHeight="1">
+    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -13656,7 +13576,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" ht="14.25" customHeight="1">
+    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -13669,7 +13589,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" ht="14.25" customHeight="1">
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -13682,7 +13602,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" ht="14.25" customHeight="1">
+    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -13695,7 +13615,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" ht="14.25" customHeight="1">
+    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -13708,7 +13628,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" ht="14.25" customHeight="1">
+    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -13721,7 +13641,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" ht="14.25" customHeight="1">
+    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -13734,7 +13654,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" ht="14.25" customHeight="1">
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -13747,7 +13667,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11" ht="14.25" customHeight="1">
+    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -13760,7 +13680,7 @@
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11" ht="14.25" customHeight="1">
+    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -13773,7 +13693,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" ht="14.25" customHeight="1">
+    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -13786,7 +13706,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11" ht="14.25" customHeight="1">
+    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -13799,7 +13719,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11" ht="14.25" customHeight="1">
+    <row r="52" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -13812,7 +13732,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11" ht="14.25" customHeight="1">
+    <row r="53" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -13825,7 +13745,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11" ht="14.25" customHeight="1">
+    <row r="54" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -13838,7 +13758,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11" ht="14.25" customHeight="1">
+    <row r="55" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -13851,7 +13771,7 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:11" ht="14.25" customHeight="1">
+    <row r="56" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -13864,7 +13784,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11" ht="14.25" customHeight="1">
+    <row r="57" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -13877,7 +13797,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11" ht="14.25" customHeight="1">
+    <row r="58" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -13890,7 +13810,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11" ht="14.25" customHeight="1">
+    <row r="59" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -13903,7 +13823,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11" ht="14.25" customHeight="1">
+    <row r="60" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -13916,7 +13836,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11" ht="14.25" customHeight="1">
+    <row r="61" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -13929,7 +13849,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11" ht="14.25" customHeight="1">
+    <row r="62" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -13942,7 +13862,7 @@
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11" ht="14.25" customHeight="1">
+    <row r="63" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -13955,7 +13875,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11" ht="14.25" customHeight="1">
+    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -13968,7 +13888,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11" ht="14.25" customHeight="1">
+    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -13981,7 +13901,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11" ht="14.25" customHeight="1">
+    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -13994,7 +13914,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:11" ht="14.25" customHeight="1">
+    <row r="67" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -14007,7 +13927,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11" ht="14.25" customHeight="1">
+    <row r="68" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -14020,7 +13940,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11" ht="14.25" customHeight="1">
+    <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -14033,7 +13953,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:11" ht="14.25" customHeight="1">
+    <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -14046,7 +13966,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:11" ht="14.25" customHeight="1">
+    <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -14059,7 +13979,7 @@
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="1:11" ht="14.25" customHeight="1">
+    <row r="72" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -14072,7 +13992,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" ht="14.25" customHeight="1">
+    <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -14085,7 +14005,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:11" ht="14.25" customHeight="1">
+    <row r="74" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -14098,7 +14018,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" ht="14.25" customHeight="1">
+    <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -14111,7 +14031,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" ht="14.25" customHeight="1">
+    <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -14124,7 +14044,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:11" ht="14.25" customHeight="1">
+    <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -14137,7 +14057,7 @@
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="1:11" ht="14.25" customHeight="1">
+    <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -14150,7 +14070,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1">
+    <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -14163,7 +14083,7 @@
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="1:11" ht="14.25" customHeight="1">
+    <row r="80" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -14176,7 +14096,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11" ht="14.25" customHeight="1">
+    <row r="81" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -14189,7 +14109,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" ht="14.25" customHeight="1">
+    <row r="82" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -14202,7 +14122,7 @@
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
     </row>
-    <row r="83" spans="1:11" ht="14.25" customHeight="1">
+    <row r="83" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -14215,7 +14135,7 @@
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
     </row>
-    <row r="84" spans="1:11" ht="14.25" customHeight="1">
+    <row r="84" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -14228,7 +14148,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
     </row>
-    <row r="85" spans="1:11" ht="14.25" customHeight="1">
+    <row r="85" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -14241,7 +14161,7 @@
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
     </row>
-    <row r="86" spans="1:11" ht="14.25" customHeight="1">
+    <row r="86" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -14254,7 +14174,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="1:11" ht="14.25" customHeight="1">
+    <row r="87" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -14267,7 +14187,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
     </row>
-    <row r="88" spans="1:11" ht="14.25" customHeight="1">
+    <row r="88" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -14280,7 +14200,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
     </row>
-    <row r="89" spans="1:11" ht="14.25" customHeight="1">
+    <row r="89" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -14293,7 +14213,7 @@
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
     </row>
-    <row r="90" spans="1:11" ht="14.25" customHeight="1">
+    <row r="90" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -14306,7 +14226,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
     </row>
-    <row r="91" spans="1:11" ht="14.25" customHeight="1">
+    <row r="91" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -14319,7 +14239,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
     </row>
-    <row r="92" spans="1:11" ht="14.25" customHeight="1">
+    <row r="92" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -14332,7 +14252,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
     </row>
-    <row r="93" spans="1:11" ht="14.25" customHeight="1">
+    <row r="93" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -14345,7 +14265,7 @@
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
     </row>
-    <row r="94" spans="1:11" ht="14.25" customHeight="1">
+    <row r="94" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -14358,7 +14278,7 @@
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
     </row>
-    <row r="95" spans="1:11" ht="14.25" customHeight="1">
+    <row r="95" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -14371,7 +14291,7 @@
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
     </row>
-    <row r="96" spans="1:11" ht="14.25" customHeight="1">
+    <row r="96" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -14384,7 +14304,7 @@
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
     </row>
-    <row r="97" spans="1:11" ht="14.25" customHeight="1">
+    <row r="97" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -14397,7 +14317,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
     </row>
-    <row r="98" spans="1:11" ht="14.25" customHeight="1">
+    <row r="98" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -14410,7 +14330,7 @@
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
     </row>
-    <row r="99" spans="1:11" ht="14.25" customHeight="1">
+    <row r="99" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -14423,7 +14343,7 @@
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
     </row>
-    <row r="100" spans="1:11" ht="14.25" customHeight="1">
+    <row r="100" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
